--- a/backend/output/Purchase_Import_Output.xlsx
+++ b/backend/output/Purchase_Import_Output.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="164" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -63,23 +63,13 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -110,7 +100,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -128,8 +118,6 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1715,7 +1703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CC56"/>
+  <dimension ref="A1:CC46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="17.625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1904,22 +1892,22 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>27AMUPA8214G1ZY</t>
+          <t>24AACCE1602K1Z3</t>
         </is>
       </c>
       <c r="B2" s="9" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>RKG25110217</t>
         </is>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>19-06-2026</t>
+          <t>11-11-2025</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>A.m. Battery Sales &amp; Service</t>
+          <t>Eagle Tradelinks Pvt.ltd.</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
@@ -1933,7 +1921,7 @@
         </is>
       </c>
       <c r="G2" s="9" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H2" s="10" t="n">
         <v>0</v>
@@ -1957,13 +1945,13 @@
         <v>0</v>
       </c>
       <c r="O2" s="10" t="n">
-        <v>6419.49</v>
+        <v>0</v>
       </c>
       <c r="P2" s="10" t="n">
-        <v>577.75</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="10" t="n">
-        <v>577.75</v>
+        <v>0</v>
       </c>
       <c r="R2" s="10" t="n">
         <v>0</v>
@@ -1978,10 +1966,10 @@
         <v>0</v>
       </c>
       <c r="V2" s="10" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="W2" s="10" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="X2" s="10" t="n">
         <v>0</v>
@@ -2054,29 +2042,29 @@
       <c r="CB2" s="11" t="n"/>
       <c r="CC2" s="11" t="inlineStr">
         <is>
-          <t>1805A.m. Battery Sales &amp; Service. Done!</t>
+          <t>RKG25110217Eagle Tradelinks Pvt.ltd.. Done!</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>27AMUPA8214G1ZY</t>
+          <t>24AACCE1602K1Z3</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>RKG25110311</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>15-11-2025</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>A.m. Battery Sales &amp; Service</t>
+          <t>Eagle Tradelinks Pvt.ltd.</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
@@ -2090,7 +2078,7 @@
         </is>
       </c>
       <c r="G3" s="9" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H3" s="10" t="n">
         <v>0</v>
@@ -2114,13 +2102,13 @@
         <v>0</v>
       </c>
       <c r="O3" s="10" t="n">
-        <v>5338.98</v>
+        <v>0</v>
       </c>
       <c r="P3" s="10" t="n">
-        <v>480.51</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="10" t="n">
-        <v>480.51</v>
+        <v>0</v>
       </c>
       <c r="R3" s="10" t="n">
         <v>0</v>
@@ -2135,10 +2123,10 @@
         <v>0</v>
       </c>
       <c r="V3" s="10" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="W3" s="10" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="X3" s="10" t="n">
         <v>0</v>
@@ -2211,29 +2199,29 @@
       <c r="CB3" s="11" t="n"/>
       <c r="CC3" s="11" t="inlineStr">
         <is>
-          <t>1806A.m. Battery Sales &amp; Service. Done!</t>
+          <t>RKG25110311Eagle Tradelinks Pvt.ltd.. Done!</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>27AMUPA8214G1ZY</t>
+          <t>24AACCE1602K1Z3</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>1807</t>
+          <t>RKG25110512</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>25-11-2025</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>A.m. Battery Sales &amp; Service</t>
+          <t>Eagle Tradelinks Pvt.ltd.</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
@@ -2247,7 +2235,7 @@
         </is>
       </c>
       <c r="G4" s="9" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H4" s="10" t="n">
         <v>0</v>
@@ -2271,13 +2259,13 @@
         <v>0</v>
       </c>
       <c r="O4" s="10" t="n">
-        <v>19258.47</v>
+        <v>0</v>
       </c>
       <c r="P4" s="10" t="n">
-        <v>1733.26</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="10" t="n">
-        <v>1733.26</v>
+        <v>0</v>
       </c>
       <c r="R4" s="10" t="n">
         <v>0</v>
@@ -2292,10 +2280,10 @@
         <v>0</v>
       </c>
       <c r="V4" s="10" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="W4" s="10" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="X4" s="10" t="n">
         <v>0</v>
@@ -2368,29 +2356,29 @@
       <c r="CB4" s="11" t="n"/>
       <c r="CC4" s="11" t="inlineStr">
         <is>
-          <t>1807A.m. Battery Sales &amp; Service. Done!</t>
+          <t>RKG25110512Eagle Tradelinks Pvt.ltd.. Done!</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>27AAXPN7718F1Z2</t>
+          <t>24AACCE1602K1Z3</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>1491</t>
+          <t>RKT25110073</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>13-07-2026</t>
+          <t>03-11-2025</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Madhuban Enterprises</t>
+          <t>Eagle Tradelinks Pvt.ltd.</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -2404,7 +2392,7 @@
         </is>
       </c>
       <c r="G5" s="9" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H5" s="10" t="n">
         <v>0</v>
@@ -2428,13 +2416,13 @@
         <v>0</v>
       </c>
       <c r="O5" s="10" t="n">
-        <v>81542.86</v>
+        <v>0</v>
       </c>
       <c r="P5" s="10" t="n">
-        <v>7338.86</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="10" t="n">
-        <v>7338.86</v>
+        <v>0</v>
       </c>
       <c r="R5" s="10" t="n">
         <v>0</v>
@@ -2449,10 +2437,10 @@
         <v>0</v>
       </c>
       <c r="V5" s="10" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="W5" s="10" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="X5" s="10" t="n">
         <v>0</v>
@@ -2525,29 +2513,29 @@
       <c r="CB5" s="11" t="n"/>
       <c r="CC5" s="11" t="inlineStr">
         <is>
-          <t>1491Madhuban Enterprises. Done!</t>
+          <t>RKT25110073Eagle Tradelinks Pvt.ltd.. Done!</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>27AAXPN7718F1Z2</t>
+          <t>24AACCE1602K1Z3</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>1840</t>
+          <t>RKT25110451</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>31-07-2026</t>
+          <t>13-11-2025</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Madhuban Enterprises</t>
+          <t>Eagle Tradelinks Pvt.ltd.</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -2561,7 +2549,7 @@
         </is>
       </c>
       <c r="G6" s="9" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H6" s="10" t="n">
         <v>0</v>
@@ -2585,13 +2573,13 @@
         <v>0</v>
       </c>
       <c r="O6" s="10" t="n">
-        <v>35651.24</v>
+        <v>0</v>
       </c>
       <c r="P6" s="10" t="n">
-        <v>3208.61</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="10" t="n">
-        <v>3208.61</v>
+        <v>0</v>
       </c>
       <c r="R6" s="10" t="n">
         <v>0</v>
@@ -2606,10 +2594,10 @@
         <v>0</v>
       </c>
       <c r="V6" s="10" t="n">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="W6" s="10" t="n">
-        <v>0</v>
+        <v>32.5</v>
       </c>
       <c r="X6" s="10" t="n">
         <v>0</v>
@@ -2682,29 +2670,29 @@
       <c r="CB6" s="11" t="n"/>
       <c r="CC6" s="11" t="inlineStr">
         <is>
-          <t>1840Madhuban Enterprises. Done!</t>
+          <t>RKT25110451Eagle Tradelinks Pvt.ltd.. Done!</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>27BRJPD4858C1ZT</t>
+          <t>27BPAPA1880C2ZG</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>DE/26-27/385</t>
+          <t>1611/OH/2025-26</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>20-07-2026</t>
+          <t>07-11-2025</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>Devansh Enterprises</t>
+          <t>Microguard Filters Corporation</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
@@ -2718,19 +2706,19 @@
         </is>
       </c>
       <c r="G7" s="9" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H7" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>9120</v>
+        <v>0</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>228</v>
+        <v>0</v>
       </c>
       <c r="K7" s="10" t="n">
-        <v>228</v>
+        <v>0</v>
       </c>
       <c r="L7" s="10" t="n">
         <v>0</v>
@@ -2742,13 +2730,13 @@
         <v>0</v>
       </c>
       <c r="O7" s="10" t="n">
-        <v>0</v>
+        <v>7940</v>
       </c>
       <c r="P7" s="10" t="n">
-        <v>0</v>
+        <v>714.6</v>
       </c>
       <c r="Q7" s="10" t="n">
-        <v>0</v>
+        <v>714.6</v>
       </c>
       <c r="R7" s="10" t="n">
         <v>0</v>
@@ -2839,29 +2827,29 @@
       <c r="CB7" s="11" t="n"/>
       <c r="CC7" s="11" t="inlineStr">
         <is>
-          <t>DE/26-27/385Devansh Enterprises. Done!</t>
+          <t>1611/OH/2025-26Microguard Filters Corporation. Done!</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>24AAEFV0191M1Z0</t>
+          <t>24ADXFS1837K1ZF</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>GST/26-27/158</t>
+          <t>2526270</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>25-07-2026</t>
+          <t>13-11-2025</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Varudi Auto Products</t>
+          <t>Spark Auto Industries</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -2932,10 +2920,10 @@
         <v>0</v>
       </c>
       <c r="Z8" s="10" t="n">
-        <v>33288</v>
+        <v>13345</v>
       </c>
       <c r="AA8" s="10" t="n">
-        <v>5991.84</v>
+        <v>2402.1</v>
       </c>
       <c r="AB8" s="10" t="n">
         <v>0</v>
@@ -2996,29 +2984,29 @@
       <c r="CB8" s="11" t="n"/>
       <c r="CC8" s="11" t="inlineStr">
         <is>
-          <t>GST/26-27/158Varudi Auto Products. Done!</t>
+          <t>2526270Spark Auto Industries. Done!</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>27AAKFS3184P1ZE</t>
+          <t>27ABKPD9591J1Z3</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>SE/5534/26-27</t>
+          <t>2526-4550</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>11-07-2026</t>
+          <t>29-11-2025</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>S B Diesel</t>
+          <t>Unique Batteries</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
@@ -3056,13 +3044,13 @@
         <v>0</v>
       </c>
       <c r="O9" s="10" t="n">
-        <v>6410.27</v>
+        <v>5588.98</v>
       </c>
       <c r="P9" s="10" t="n">
-        <v>576.92</v>
+        <v>503.01</v>
       </c>
       <c r="Q9" s="10" t="n">
-        <v>576.92</v>
+        <v>503.01</v>
       </c>
       <c r="R9" s="10" t="n">
         <v>0</v>
@@ -3153,29 +3141,29 @@
       <c r="CB9" s="11" t="n"/>
       <c r="CC9" s="11" t="inlineStr">
         <is>
-          <t>SE/5534/26-27S B Diesel. Done!</t>
+          <t>2526-4550Unique Batteries. Done!</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>27AAKFS3184P1ZE</t>
+          <t>27AALCP3764A1ZF</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>SE/6670/26-27</t>
+          <t>25-26/GST604</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>28-07-2026</t>
+          <t>07-11-2025</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>S B Diesel</t>
+          <t>Power Link Gensets Private Limited</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
@@ -3213,13 +3201,13 @@
         <v>0</v>
       </c>
       <c r="O10" s="10" t="n">
-        <v>60948.85</v>
+        <v>27643.22</v>
       </c>
       <c r="P10" s="10" t="n">
-        <v>5485.39</v>
+        <v>2487.89</v>
       </c>
       <c r="Q10" s="10" t="n">
-        <v>5485.39</v>
+        <v>2487.89</v>
       </c>
       <c r="R10" s="10" t="n">
         <v>0</v>
@@ -3310,29 +3298,29 @@
       <c r="CB10" s="11" t="n"/>
       <c r="CC10" s="11" t="inlineStr">
         <is>
-          <t>SE/6670/26-27S B Diesel. Done!</t>
+          <t>25-26/GST604Power Link Gensets Private Limited. Done!</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>27AAKFS3184P1ZE</t>
+          <t>27AILPP4508M1ZQ</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>SE/6678/26-27</t>
+          <t>SG-18565</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>28-07-2026</t>
+          <t>25-11-2025</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>S B Diesel</t>
+          <t>Bhavesh Tractor And Earth Movers</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
@@ -3370,13 +3358,13 @@
         <v>0</v>
       </c>
       <c r="O11" s="10" t="n">
-        <v>7082.99</v>
+        <v>20597</v>
       </c>
       <c r="P11" s="10" t="n">
-        <v>637.47</v>
+        <v>1853.73</v>
       </c>
       <c r="Q11" s="10" t="n">
-        <v>637.47</v>
+        <v>1853.73</v>
       </c>
       <c r="R11" s="10" t="n">
         <v>0</v>
@@ -3467,29 +3455,29 @@
       <c r="CB11" s="11" t="n"/>
       <c r="CC11" s="11" t="inlineStr">
         <is>
-          <t>SE/6678/26-27S B Diesel. Done!</t>
+          <t>SG-18565Bhavesh Tractor And Earth Movers. Done!</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>03ADDPV7313D1ZV</t>
+          <t>24AAEFV0191M1Z0</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>GT/184</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>15-07-2026</t>
+          <t>20-11-2025</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>Virk Brothers</t>
+          <t>Varudi Auto Products</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -3560,10 +3548,10 @@
         <v>0</v>
       </c>
       <c r="Z12" s="10" t="n">
-        <v>16665</v>
+        <v>37726</v>
       </c>
       <c r="AA12" s="10" t="n">
-        <v>3000</v>
+        <v>6790.68</v>
       </c>
       <c r="AB12" s="10" t="n">
         <v>0</v>
@@ -3624,29 +3612,29 @@
       <c r="CB12" s="11" t="n"/>
       <c r="CC12" s="11" t="inlineStr">
         <is>
-          <t>1771Virk Brothers. Done!</t>
+          <t>GT/184Varudi Auto Products. Done!</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>27AHXPG7701J1ZV</t>
+          <t>24ADKFS9502N1ZK</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>IC/26-27/0586</t>
+          <t>784/2025-26</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>09-06-2026</t>
+          <t>05-11-2025</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Innovatech Corporation</t>
+          <t>Sps Techno Circuits LLP</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -3684,13 +3672,13 @@
         <v>0</v>
       </c>
       <c r="O13" s="10" t="n">
-        <v>1300</v>
+        <v>0</v>
       </c>
       <c r="P13" s="10" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="10" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="R13" s="10" t="n">
         <v>0</v>
@@ -3717,10 +3705,10 @@
         <v>0</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>0</v>
+        <v>7650</v>
       </c>
       <c r="AA13" s="10" t="n">
-        <v>0</v>
+        <v>1377</v>
       </c>
       <c r="AB13" s="10" t="n">
         <v>0</v>
@@ -3781,29 +3769,29 @@
       <c r="CB13" s="11" t="n"/>
       <c r="CC13" s="11" t="inlineStr">
         <is>
-          <t>IC/26-27/0586Innovatech Corporation. Done!</t>
+          <t>784/2025-26Sps Techno Circuits LLP. Done!</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>27AHXPG7701J1ZV</t>
+          <t>27CDWPP9097D1ZL</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>IC/26-27/0634</t>
+          <t>EC/064/2025-26</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>15-06-2026</t>
+          <t>15-11-2025</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>Innovatech Corporation</t>
+          <t>Expert Computers</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
@@ -3841,13 +3829,13 @@
         <v>0</v>
       </c>
       <c r="O14" s="10" t="n">
-        <v>5200</v>
+        <v>33050.84</v>
       </c>
       <c r="P14" s="10" t="n">
-        <v>468</v>
+        <v>2974.58</v>
       </c>
       <c r="Q14" s="10" t="n">
-        <v>468</v>
+        <v>2974.58</v>
       </c>
       <c r="R14" s="10" t="n">
         <v>0</v>
@@ -3938,29 +3926,29 @@
       <c r="CB14" s="11" t="n"/>
       <c r="CC14" s="11" t="inlineStr">
         <is>
-          <t>IC/26-27/0634Innovatech Corporation. Done!</t>
+          <t>EC/064/2025-26Expert Computers. Done!</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>27AALCP3764A1ZF</t>
+          <t>03AABFR7311L1ZD</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>26-27/GST332</t>
+          <t>3319</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>21-07-2026</t>
+          <t>14-11-2025</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Power Link Gensets Private Limited</t>
+          <t>Raj Agencies</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
@@ -3998,13 +3986,13 @@
         <v>0</v>
       </c>
       <c r="O15" s="10" t="n">
-        <v>97457.63</v>
+        <v>0</v>
       </c>
       <c r="P15" s="10" t="n">
-        <v>8771.190000000001</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="10" t="n">
-        <v>8771.190000000001</v>
+        <v>0</v>
       </c>
       <c r="R15" s="10" t="n">
         <v>0</v>
@@ -4031,10 +4019,10 @@
         <v>0</v>
       </c>
       <c r="Z15" s="10" t="n">
-        <v>0</v>
+        <v>34884</v>
       </c>
       <c r="AA15" s="10" t="n">
-        <v>0</v>
+        <v>6279</v>
       </c>
       <c r="AB15" s="10" t="n">
         <v>0</v>
@@ -4095,29 +4083,29 @@
       <c r="CB15" s="11" t="n"/>
       <c r="CC15" s="11" t="inlineStr">
         <is>
-          <t>26-27/GST332Power Link Gensets Private Limited. Done!</t>
+          <t>3319Raj Agencies. Done!</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>27AALCP3764A1ZF</t>
+          <t>27AAKFS3184P1ZE</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>26-27/GST359</t>
+          <t>SE/13176/25-26</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>28-07-2026</t>
+          <t>01-11-2025</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Power Link Gensets Private Limited</t>
+          <t>S B Diesel</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
@@ -4155,13 +4143,13 @@
         <v>0</v>
       </c>
       <c r="O16" s="10" t="n">
-        <v>224576.27</v>
+        <v>18336.65</v>
       </c>
       <c r="P16" s="10" t="n">
-        <v>20211.86</v>
+        <v>1650.3</v>
       </c>
       <c r="Q16" s="10" t="n">
-        <v>20211.86</v>
+        <v>1650.3</v>
       </c>
       <c r="R16" s="10" t="n">
         <v>0</v>
@@ -4252,29 +4240,29 @@
       <c r="CB16" s="11" t="n"/>
       <c r="CC16" s="11" t="inlineStr">
         <is>
-          <t>26-27/GST359Power Link Gensets Private Limited. Done!</t>
+          <t>SE/13176/25-26S B Diesel. Done!</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>24AAICV6161A1ZL</t>
+          <t>27AAKFS3184P1ZE</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>161/VZC/26-27</t>
+          <t>SE/13177/25-26</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>16-07-2026</t>
+          <t>01-11-2025</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Vanza Controls Private Limited</t>
+          <t>S B Diesel</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
@@ -4312,13 +4300,13 @@
         <v>0</v>
       </c>
       <c r="O17" s="10" t="n">
-        <v>0</v>
+        <v>20841.38</v>
       </c>
       <c r="P17" s="10" t="n">
-        <v>0</v>
+        <v>1875.73</v>
       </c>
       <c r="Q17" s="10" t="n">
-        <v>0</v>
+        <v>1875.73</v>
       </c>
       <c r="R17" s="10" t="n">
         <v>0</v>
@@ -4345,10 +4333,10 @@
         <v>0</v>
       </c>
       <c r="Z17" s="10" t="n">
-        <v>4400</v>
+        <v>0</v>
       </c>
       <c r="AA17" s="10" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="AB17" s="10" t="n">
         <v>0</v>
@@ -4409,29 +4397,29 @@
       <c r="CB17" s="11" t="n"/>
       <c r="CC17" s="11" t="inlineStr">
         <is>
-          <t>161/VZC/26-27Vanza Controls Private Limited. Done!</t>
+          <t>SE/13177/25-26S B Diesel. Done!</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>27AILPP4508M1ZQ</t>
+          <t>27AAKFS3184P1ZE</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>SG-19982</t>
+          <t>SE/14051/25-26</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>09-07-2026</t>
+          <t>15-11-2025</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Bhavesh Tractor And Earth Movers</t>
+          <t>S B Diesel</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
@@ -4469,13 +4457,13 @@
         <v>0</v>
       </c>
       <c r="O18" s="10" t="n">
-        <v>15645</v>
+        <v>10846.21</v>
       </c>
       <c r="P18" s="10" t="n">
-        <v>1408.05</v>
+        <v>976.16</v>
       </c>
       <c r="Q18" s="10" t="n">
-        <v>1408.05</v>
+        <v>976.16</v>
       </c>
       <c r="R18" s="10" t="n">
         <v>0</v>
@@ -4566,29 +4554,29 @@
       <c r="CB18" s="11" t="n"/>
       <c r="CC18" s="11" t="inlineStr">
         <is>
-          <t>SG-19982Bhavesh Tractor And Earth Movers. Done!</t>
+          <t>SE/14051/25-26S B Diesel. Done!</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>27AILPP4508M1ZQ</t>
+          <t>27AAKFS3184P1ZE</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>SG-20008</t>
+          <t>SE/14052/25-26</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>13-07-2026</t>
+          <t>15-11-2025</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Bhavesh Tractor And Earth Movers</t>
+          <t>S B Diesel</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
@@ -4626,13 +4614,13 @@
         <v>0</v>
       </c>
       <c r="O19" s="10" t="n">
-        <v>19604</v>
+        <v>3626.88</v>
       </c>
       <c r="P19" s="10" t="n">
-        <v>1764.36</v>
+        <v>326.42</v>
       </c>
       <c r="Q19" s="10" t="n">
-        <v>1764.36</v>
+        <v>326.42</v>
       </c>
       <c r="R19" s="10" t="n">
         <v>0</v>
@@ -4723,29 +4711,29 @@
       <c r="CB19" s="11" t="n"/>
       <c r="CC19" s="11" t="inlineStr">
         <is>
-          <t>SG-20008Bhavesh Tractor And Earth Movers. Done!</t>
+          <t>SE/14052/25-26S B Diesel. Done!</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>27AILPP4508M1ZQ</t>
+          <t>27AAKFS3184P1ZE</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>SG-20049</t>
+          <t>SE/14760/25-26</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>16-07-2026</t>
+          <t>27-11-2025</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Bhavesh Tractor And Earth Movers</t>
+          <t>S B Diesel</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
@@ -4783,13 +4771,13 @@
         <v>0</v>
       </c>
       <c r="O20" s="10" t="n">
-        <v>7650</v>
+        <v>5663.84</v>
       </c>
       <c r="P20" s="10" t="n">
-        <v>688.5</v>
+        <v>509.75</v>
       </c>
       <c r="Q20" s="10" t="n">
-        <v>688.5</v>
+        <v>509.75</v>
       </c>
       <c r="R20" s="10" t="n">
         <v>0</v>
@@ -4880,29 +4868,29 @@
       <c r="CB20" s="11" t="n"/>
       <c r="CC20" s="11" t="inlineStr">
         <is>
-          <t>SG-20049Bhavesh Tractor And Earth Movers. Done!</t>
+          <t>SE/14760/25-26S B Diesel. Done!</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>26AAHFG0858R1ZS</t>
+          <t>27AAKFS3184P1ZE</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>GPE/1231/26-27</t>
+          <t>SE/14761/25-26</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>04-07-2026</t>
+          <t>27-11-2025</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Goel Power Engineers LLP</t>
+          <t>S B Diesel</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
@@ -4940,13 +4928,13 @@
         <v>0</v>
       </c>
       <c r="O21" s="10" t="n">
-        <v>0</v>
+        <v>13646.32</v>
       </c>
       <c r="P21" s="10" t="n">
-        <v>0</v>
+        <v>1228.17</v>
       </c>
       <c r="Q21" s="10" t="n">
-        <v>0</v>
+        <v>1228.17</v>
       </c>
       <c r="R21" s="10" t="n">
         <v>0</v>
@@ -4973,10 +4961,10 @@
         <v>0</v>
       </c>
       <c r="Z21" s="10" t="n">
-        <v>302400</v>
+        <v>0</v>
       </c>
       <c r="AA21" s="10" t="n">
-        <v>54432</v>
+        <v>0</v>
       </c>
       <c r="AB21" s="10" t="n">
         <v>0</v>
@@ -5037,29 +5025,29 @@
       <c r="CB21" s="11" t="n"/>
       <c r="CC21" s="11" t="inlineStr">
         <is>
-          <t>GPE/1231/26-27Goel Power Engineers LLP. Done!</t>
+          <t>SE/14761/25-26S B Diesel. Done!</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>26AAHFG0858R1ZS</t>
+          <t>24AAHFJ5991L1ZT</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>GPE/1239/26-27</t>
+          <t>GT/37</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>15-10-2025</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Goel Power Engineers LLP</t>
+          <t>J.p.diesel</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
@@ -5130,10 +5118,10 @@
         <v>0</v>
       </c>
       <c r="Z22" s="10" t="n">
-        <v>1100400</v>
+        <v>100000</v>
       </c>
       <c r="AA22" s="10" t="n">
-        <v>198072</v>
+        <v>18000</v>
       </c>
       <c r="AB22" s="10" t="n">
         <v>0</v>
@@ -5194,29 +5182,29 @@
       <c r="CB22" s="11" t="n"/>
       <c r="CC22" s="11" t="inlineStr">
         <is>
-          <t>GPE/1239/26-27Goel Power Engineers LLP. Done!</t>
+          <t>GT/37J.p.diesel. Done!</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>26AAHFG0858R1ZS</t>
+          <t>27AHXPG7701J1ZV</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>GPE/1240/26-27</t>
+          <t>IC/25-26/1776</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>04-11-2025</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Goel Power Engineers LLP</t>
+          <t>Innovatech Corporation</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
@@ -5254,13 +5242,13 @@
         <v>0</v>
       </c>
       <c r="O23" s="10" t="n">
-        <v>0</v>
+        <v>10220</v>
       </c>
       <c r="P23" s="10" t="n">
-        <v>0</v>
+        <v>919.8</v>
       </c>
       <c r="Q23" s="10" t="n">
-        <v>0</v>
+        <v>919.8</v>
       </c>
       <c r="R23" s="10" t="n">
         <v>0</v>
@@ -5287,10 +5275,10 @@
         <v>0</v>
       </c>
       <c r="Z23" s="10" t="n">
-        <v>290850</v>
+        <v>0</v>
       </c>
       <c r="AA23" s="10" t="n">
-        <v>52353</v>
+        <v>0</v>
       </c>
       <c r="AB23" s="10" t="n">
         <v>0</v>
@@ -5351,29 +5339,29 @@
       <c r="CB23" s="11" t="n"/>
       <c r="CC23" s="11" t="inlineStr">
         <is>
-          <t>GPE/1240/26-27Goel Power Engineers LLP. Done!</t>
+          <t>IC/25-26/1776Innovatech Corporation. Done!</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>26AAHFG0858R1ZS</t>
+          <t>27AHXPG7701J1ZV</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>GPE/1308/26-27</t>
+          <t>IC/25-26/1832</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>10-07-2026</t>
+          <t>10-11-2025</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Goel Power Engineers LLP</t>
+          <t>Innovatech Corporation</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
@@ -5411,13 +5399,13 @@
         <v>0</v>
       </c>
       <c r="O24" s="10" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="P24" s="10" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="Q24" s="10" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="R24" s="10" t="n">
         <v>0</v>
@@ -5444,10 +5432,10 @@
         <v>0</v>
       </c>
       <c r="Z24" s="10" t="n">
-        <v>325500</v>
+        <v>0</v>
       </c>
       <c r="AA24" s="10" t="n">
-        <v>58590</v>
+        <v>0</v>
       </c>
       <c r="AB24" s="10" t="n">
         <v>0</v>
@@ -5508,29 +5496,29 @@
       <c r="CB24" s="11" t="n"/>
       <c r="CC24" s="11" t="inlineStr">
         <is>
-          <t>GPE/1308/26-27Goel Power Engineers LLP. Done!</t>
+          <t>IC/25-26/1832Innovatech Corporation. Done!</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>26AAHFG0858R1ZS</t>
+          <t>27AHXPG7701J1ZV</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>GPE/1311/26-27</t>
+          <t>IC/25-26/1874</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>10-07-2026</t>
+          <t>14-11-2025</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Goel Power Engineers LLP</t>
+          <t>Innovatech Corporation</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
@@ -5568,13 +5556,13 @@
         <v>0</v>
       </c>
       <c r="O25" s="10" t="n">
-        <v>0</v>
+        <v>6800</v>
       </c>
       <c r="P25" s="10" t="n">
-        <v>0</v>
+        <v>612</v>
       </c>
       <c r="Q25" s="10" t="n">
-        <v>0</v>
+        <v>612</v>
       </c>
       <c r="R25" s="10" t="n">
         <v>0</v>
@@ -5601,10 +5589,10 @@
         <v>0</v>
       </c>
       <c r="Z25" s="10" t="n">
-        <v>480000</v>
+        <v>0</v>
       </c>
       <c r="AA25" s="10" t="n">
-        <v>86400</v>
+        <v>0</v>
       </c>
       <c r="AB25" s="10" t="n">
         <v>0</v>
@@ -5665,29 +5653,29 @@
       <c r="CB25" s="11" t="n"/>
       <c r="CC25" s="11" t="inlineStr">
         <is>
-          <t>GPE/1311/26-27Goel Power Engineers LLP. Done!</t>
+          <t>IC/25-26/1874Innovatech Corporation. Done!</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>26AAHFG0858R1ZS</t>
+          <t>24ABUPD5630N1ZB</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>GPE/1458/26-27</t>
+          <t>GT/741</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>21-07-2026</t>
+          <t>03-11-2025</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Goel Power Engineers LLP</t>
+          <t>Davda Sales And Service</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
@@ -5758,10 +5746,10 @@
         <v>0</v>
       </c>
       <c r="Z26" s="10" t="n">
-        <v>339500</v>
+        <v>9694.59</v>
       </c>
       <c r="AA26" s="10" t="n">
-        <v>61110</v>
+        <v>1745.03</v>
       </c>
       <c r="AB26" s="10" t="n">
         <v>0</v>
@@ -5822,29 +5810,29 @@
       <c r="CB26" s="11" t="n"/>
       <c r="CC26" s="11" t="inlineStr">
         <is>
-          <t>GPE/1458/26-27Goel Power Engineers LLP. Done!</t>
+          <t>GT/741Davda Sales And Service. Done!</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>26AAHFG0858R1ZS</t>
+          <t>27AAXPN7718F1Z2</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>GPE/1459/26-27</t>
+          <t>3463</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>21-07-2026</t>
+          <t>07-11-2025</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Goel Power Engineers LLP</t>
+          <t>Madhuban Enterprises</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
@@ -5882,13 +5870,13 @@
         <v>0</v>
       </c>
       <c r="O27" s="10" t="n">
-        <v>0</v>
+        <v>26708.91</v>
       </c>
       <c r="P27" s="10" t="n">
-        <v>0</v>
+        <v>2403.79</v>
       </c>
       <c r="Q27" s="10" t="n">
-        <v>0</v>
+        <v>2403.79</v>
       </c>
       <c r="R27" s="10" t="n">
         <v>0</v>
@@ -5915,10 +5903,10 @@
         <v>0</v>
       </c>
       <c r="Z27" s="10" t="n">
-        <v>612500</v>
+        <v>0</v>
       </c>
       <c r="AA27" s="10" t="n">
-        <v>110250</v>
+        <v>0</v>
       </c>
       <c r="AB27" s="10" t="n">
         <v>0</v>
@@ -5979,29 +5967,29 @@
       <c r="CB27" s="11" t="n"/>
       <c r="CC27" s="11" t="inlineStr">
         <is>
-          <t>GPE/1459/26-27Goel Power Engineers LLP. Done!</t>
+          <t>3463Madhuban Enterprises. Done!</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>26AAHFG0858R1ZS</t>
+          <t>27ABAFA7278F1ZE</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>GPE/1481/26-27</t>
+          <t>AT/25-26/1963</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>22-07-2026</t>
+          <t>17-11-2025</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Goel Power Engineers LLP</t>
+          <t>Asrav Tyres</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
@@ -6039,13 +6027,13 @@
         <v>0</v>
       </c>
       <c r="O28" s="10" t="n">
-        <v>0</v>
+        <v>10286.5</v>
       </c>
       <c r="P28" s="10" t="n">
-        <v>0</v>
+        <v>925.79</v>
       </c>
       <c r="Q28" s="10" t="n">
-        <v>0</v>
+        <v>925.79</v>
       </c>
       <c r="R28" s="10" t="n">
         <v>0</v>
@@ -6072,10 +6060,10 @@
         <v>0</v>
       </c>
       <c r="Z28" s="10" t="n">
-        <v>302400</v>
+        <v>0</v>
       </c>
       <c r="AA28" s="10" t="n">
-        <v>54432</v>
+        <v>0</v>
       </c>
       <c r="AB28" s="10" t="n">
         <v>0</v>
@@ -6136,29 +6124,29 @@
       <c r="CB28" s="11" t="n"/>
       <c r="CC28" s="11" t="inlineStr">
         <is>
-          <t>GPE/1481/26-27Goel Power Engineers LLP. Done!</t>
+          <t>AT/25-26/1963Asrav Tyres. Done!</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>26AAHFG0858R1ZS</t>
+          <t>24AAHFJ5991L1ZT</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>GPE/1482/26-27</t>
+          <t>GT/40</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>22-07-2026</t>
+          <t>11-11-2025</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Goel Power Engineers LLP</t>
+          <t>J.p.diesel</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
@@ -6229,10 +6217,10 @@
         <v>0</v>
       </c>
       <c r="Z29" s="10" t="n">
-        <v>1105400</v>
+        <v>3200</v>
       </c>
       <c r="AA29" s="10" t="n">
-        <v>198972</v>
+        <v>576</v>
       </c>
       <c r="AB29" s="10" t="n">
         <v>0</v>
@@ -6293,29 +6281,29 @@
       <c r="CB29" s="11" t="n"/>
       <c r="CC29" s="11" t="inlineStr">
         <is>
-          <t>GPE/1482/26-27Goel Power Engineers LLP. Done!</t>
+          <t>GT/40J.p.diesel. Done!</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>26AAHFG0858R1ZS</t>
+          <t>24AAHFJ5991L1ZT</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>GPE/1537/26-27</t>
+          <t>GT/41</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>28-07-2026</t>
+          <t>15-11-2025</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>Goel Power Engineers LLP</t>
+          <t>J.p.diesel</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
@@ -6386,10 +6374,10 @@
         <v>0</v>
       </c>
       <c r="Z30" s="10" t="n">
-        <v>478800</v>
+        <v>1563</v>
       </c>
       <c r="AA30" s="10" t="n">
-        <v>86184</v>
+        <v>281</v>
       </c>
       <c r="AB30" s="10" t="n">
         <v>0</v>
@@ -6450,29 +6438,29 @@
       <c r="CB30" s="11" t="n"/>
       <c r="CC30" s="11" t="inlineStr">
         <is>
-          <t>GPE/1537/26-27Goel Power Engineers LLP. Done!</t>
+          <t>GT/41J.p.diesel. Done!</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>26AAHFG0858R1ZS</t>
+          <t>24AAHFJ5991L1ZT</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>GPE/1616/26-27</t>
+          <t>GT/42</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>31-07-2026</t>
+          <t>25-11-2025</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>Goel Power Engineers LLP</t>
+          <t>J.p.diesel</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
@@ -6543,10 +6531,10 @@
         <v>0</v>
       </c>
       <c r="Z31" s="10" t="n">
-        <v>547750</v>
+        <v>3350</v>
       </c>
       <c r="AA31" s="10" t="n">
-        <v>98595</v>
+        <v>603</v>
       </c>
       <c r="AB31" s="10" t="n">
         <v>0</v>
@@ -6607,29 +6595,29 @@
       <c r="CB31" s="11" t="n"/>
       <c r="CC31" s="11" t="inlineStr">
         <is>
-          <t>GPE/1616/26-27Goel Power Engineers LLP. Done!</t>
+          <t>GT/42J.p.diesel. Done!</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>26AAHFG0858R1ZS</t>
+          <t>24AAHFS3107M1Z6</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>GPE/1617/26-27</t>
+          <t>901</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>31-07-2026</t>
+          <t>15-11-2025</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>Goel Power Engineers LLP</t>
+          <t>Swastik Manufacturers</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
@@ -6700,10 +6688,10 @@
         <v>0</v>
       </c>
       <c r="Z32" s="10" t="n">
-        <v>339500</v>
+        <v>23415</v>
       </c>
       <c r="AA32" s="10" t="n">
-        <v>61110</v>
+        <v>4214.7</v>
       </c>
       <c r="AB32" s="10" t="n">
         <v>0</v>
@@ -6764,29 +6752,29 @@
       <c r="CB32" s="11" t="n"/>
       <c r="CC32" s="11" t="inlineStr">
         <is>
-          <t>GPE/1617/26-27Goel Power Engineers LLP. Done!</t>
+          <t>901Swastik Manufacturers. Done!</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>26AAHFG0858R1ZS</t>
+          <t>27ABCPM0164G1ZY</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>GPE/1618/26-27</t>
+          <t>75</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>31-07-2026</t>
+          <t>26-11-2025</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>Goel Power Engineers LLP</t>
+          <t>Eco Scrap And Processing</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
@@ -6824,13 +6812,13 @@
         <v>0</v>
       </c>
       <c r="O33" s="10" t="n">
-        <v>0</v>
+        <v>180000</v>
       </c>
       <c r="P33" s="10" t="n">
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="Q33" s="10" t="n">
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="R33" s="10" t="n">
         <v>0</v>
@@ -6857,10 +6845,10 @@
         <v>0</v>
       </c>
       <c r="Z33" s="10" t="n">
-        <v>612500</v>
+        <v>0</v>
       </c>
       <c r="AA33" s="10" t="n">
-        <v>110250</v>
+        <v>0</v>
       </c>
       <c r="AB33" s="10" t="n">
         <v>0</v>
@@ -6921,29 +6909,29 @@
       <c r="CB33" s="11" t="n"/>
       <c r="CC33" s="11" t="inlineStr">
         <is>
-          <t>GPE/1618/26-27Goel Power Engineers LLP. Done!</t>
+          <t>75Eco Scrap And Processing. Done!</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>24ADKFS9502N1ZK</t>
+          <t>27AAKFN4046M1ZU</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>306/2026-27</t>
+          <t>3956/BC/25-26</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>04-07-2026</t>
+          <t>12-11-2025</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>Sps Techno Circuits LLP</t>
+          <t>Nhp Powersystems LLP</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
@@ -6981,13 +6969,13 @@
         <v>0</v>
       </c>
       <c r="O34" s="10" t="n">
-        <v>0</v>
+        <v>19125</v>
       </c>
       <c r="P34" s="10" t="n">
-        <v>0</v>
+        <v>1721.25</v>
       </c>
       <c r="Q34" s="10" t="n">
-        <v>0</v>
+        <v>1721.25</v>
       </c>
       <c r="R34" s="10" t="n">
         <v>0</v>
@@ -7014,10 +7002,10 @@
         <v>0</v>
       </c>
       <c r="Z34" s="10" t="n">
-        <v>21520</v>
+        <v>0</v>
       </c>
       <c r="AA34" s="10" t="n">
-        <v>3873.6</v>
+        <v>0</v>
       </c>
       <c r="AB34" s="10" t="n">
         <v>0</v>
@@ -7078,29 +7066,29 @@
       <c r="CB34" s="11" t="n"/>
       <c r="CC34" s="11" t="inlineStr">
         <is>
-          <t>306/2026-27Sps Techno Circuits LLP. Done!</t>
+          <t>3956/BC/25-26Nhp Powersystems LLP. Done!</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>24ADKFS9502N1ZK</t>
+          <t>26AAHFG0858R1ZS</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>392/2026-27</t>
+          <t>GPE/2543/25-26</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>29-07-2026</t>
+          <t>03-11-2025</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>Sps Techno Circuits LLP</t>
+          <t>Goel Power Engineers LLP</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
@@ -7171,10 +7159,10 @@
         <v>0</v>
       </c>
       <c r="Z35" s="10" t="n">
-        <v>19100</v>
+        <v>407550</v>
       </c>
       <c r="AA35" s="10" t="n">
-        <v>3438</v>
+        <v>73359</v>
       </c>
       <c r="AB35" s="10" t="n">
         <v>0</v>
@@ -7235,29 +7223,29 @@
       <c r="CB35" s="11" t="n"/>
       <c r="CC35" s="11" t="inlineStr">
         <is>
-          <t>392/2026-27Sps Techno Circuits LLP. Done!</t>
+          <t>GPE/2543/25-26Goel Power Engineers LLP. Done!</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>24AAUFA9472E1Z4</t>
+          <t>26AAHFG0858R1ZS</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>AP/586/26-27</t>
+          <t>GPE/2544/25-26</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>27-07-2026</t>
+          <t>03-11-2025</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>A Top Power</t>
+          <t>Goel Power Engineers LLP</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
@@ -7328,10 +7316,10 @@
         <v>0</v>
       </c>
       <c r="Z36" s="10" t="n">
-        <v>11975</v>
+        <v>473880</v>
       </c>
       <c r="AA36" s="10" t="n">
-        <v>2155.5</v>
+        <v>85298.39999999999</v>
       </c>
       <c r="AB36" s="10" t="n">
         <v>0</v>
@@ -7392,29 +7380,29 @@
       <c r="CB36" s="11" t="n"/>
       <c r="CC36" s="11" t="inlineStr">
         <is>
-          <t>AP/586/26-27A Top Power. Done!</t>
+          <t>GPE/2544/25-26Goel Power Engineers LLP. Done!</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>03AABFR7311L1ZD</t>
+          <t>26AAHFG0858R1ZS</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>3566</t>
+          <t>GPE/2552/25-26</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>31-07-2026</t>
+          <t>04-11-2025</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Raj Agencies</t>
+          <t>Goel Power Engineers LLP</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
@@ -7485,10 +7473,10 @@
         <v>0</v>
       </c>
       <c r="Z37" s="10" t="n">
-        <v>42620</v>
+        <v>490880</v>
       </c>
       <c r="AA37" s="10" t="n">
-        <v>7672</v>
+        <v>88358.39999999999</v>
       </c>
       <c r="AB37" s="10" t="n">
         <v>0</v>
@@ -7549,29 +7537,29 @@
       <c r="CB37" s="11" t="n"/>
       <c r="CC37" s="11" t="inlineStr">
         <is>
-          <t>3566Raj Agencies. Done!</t>
+          <t>GPE/2552/25-26Goel Power Engineers LLP. Done!</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>27ABAFA7278F1ZE</t>
+          <t>26AAHFG0858R1ZS</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>AT/26-27/1171</t>
+          <t>GPE/2579/25-26</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>24-07-2026</t>
+          <t>07-11-2025</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Asrav Tyres</t>
+          <t>Goel Power Engineers LLP</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
@@ -7609,13 +7597,13 @@
         <v>0</v>
       </c>
       <c r="O38" s="10" t="n">
-        <v>7970.5</v>
+        <v>0</v>
       </c>
       <c r="P38" s="10" t="n">
-        <v>717.35</v>
+        <v>0</v>
       </c>
       <c r="Q38" s="10" t="n">
-        <v>717.35</v>
+        <v>0</v>
       </c>
       <c r="R38" s="10" t="n">
         <v>0</v>
@@ -7642,10 +7630,10 @@
         <v>0</v>
       </c>
       <c r="Z38" s="10" t="n">
-        <v>0</v>
+        <v>337920</v>
       </c>
       <c r="AA38" s="10" t="n">
-        <v>0</v>
+        <v>60825.6</v>
       </c>
       <c r="AB38" s="10" t="n">
         <v>0</v>
@@ -7706,29 +7694,29 @@
       <c r="CB38" s="11" t="n"/>
       <c r="CC38" s="11" t="inlineStr">
         <is>
-          <t>AT/26-27/1171Asrav Tyres. Done!</t>
+          <t>GPE/2579/25-26Goel Power Engineers LLP. Done!</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>09AAACI0049N1ZG</t>
+          <t>26AAHFG0858R1ZS</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>PSI-2627-01999</t>
+          <t>GPE/2640/25-26</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>20-07-2026</t>
+          <t>14-11-2025</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>M/s Insel Rectifiers India Pvt.ltd.</t>
+          <t>Goel Power Engineers LLP</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
@@ -7799,10 +7787,10 @@
         <v>0</v>
       </c>
       <c r="Z39" s="10" t="n">
-        <v>38800</v>
+        <v>1905000</v>
       </c>
       <c r="AA39" s="10" t="n">
-        <v>6984</v>
+        <v>342900</v>
       </c>
       <c r="AB39" s="10" t="n">
         <v>0</v>
@@ -7863,29 +7851,29 @@
       <c r="CB39" s="11" t="n"/>
       <c r="CC39" s="11" t="inlineStr">
         <is>
-          <t>PSI-2627-01999M/s Insel Rectifiers India Pvt.ltd.. Done!</t>
+          <t>GPE/2640/25-26Goel Power Engineers LLP. Done!</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>09AAACI0049N1ZG</t>
+          <t>26AAHFG0858R1ZS</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>PSI-2627-02002</t>
+          <t>GPE/2647/25-26</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>20-07-2026</t>
+          <t>15-11-2025</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>M/s Insel Rectifiers India Pvt.ltd.</t>
+          <t>Goel Power Engineers LLP</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
@@ -7956,10 +7944,10 @@
         <v>0</v>
       </c>
       <c r="Z40" s="10" t="n">
-        <v>54600</v>
+        <v>593340</v>
       </c>
       <c r="AA40" s="10" t="n">
-        <v>9828</v>
+        <v>106801.2</v>
       </c>
       <c r="AB40" s="10" t="n">
         <v>0</v>
@@ -8020,29 +8008,29 @@
       <c r="CB40" s="11" t="n"/>
       <c r="CC40" s="11" t="inlineStr">
         <is>
-          <t>PSI-2627-02002M/s Insel Rectifiers India Pvt.ltd.. Done!</t>
+          <t>GPE/2647/25-26Goel Power Engineers LLP. Done!</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>27BPAPA1880C2ZG</t>
+          <t>26AAHFG0858R1ZS</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>0841/OH/2026-27</t>
+          <t>GPE/2683/25-26</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>13-07-2026</t>
+          <t>19-11-2025</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>Microguard Filters Corporation</t>
+          <t>Goel Power Engineers LLP</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
@@ -8080,13 +8068,13 @@
         <v>0</v>
       </c>
       <c r="O41" s="10" t="n">
-        <v>17530</v>
+        <v>0</v>
       </c>
       <c r="P41" s="10" t="n">
-        <v>1577.7</v>
+        <v>0</v>
       </c>
       <c r="Q41" s="10" t="n">
-        <v>1577.7</v>
+        <v>0</v>
       </c>
       <c r="R41" s="10" t="n">
         <v>0</v>
@@ -8113,10 +8101,10 @@
         <v>0</v>
       </c>
       <c r="Z41" s="10" t="n">
-        <v>0</v>
+        <v>593340</v>
       </c>
       <c r="AA41" s="10" t="n">
-        <v>0</v>
+        <v>106801.2</v>
       </c>
       <c r="AB41" s="10" t="n">
         <v>0</v>
@@ -8177,29 +8165,29 @@
       <c r="CB41" s="11" t="n"/>
       <c r="CC41" s="11" t="inlineStr">
         <is>
-          <t>0841/OH/2026-27Microguard Filters Corporation. Done!</t>
+          <t>GPE/2683/25-26Goel Power Engineers LLP. Done!</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>27AHXPG7701J1ZV</t>
+          <t>26AAHFG0858R1ZS</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>IC/26-27/0904</t>
+          <t>GPE/2684/25-26</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>11-07-2026</t>
+          <t>19-11-2025</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>Innovatech Corporation</t>
+          <t>Goel Power Engineers LLP</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
@@ -8237,13 +8225,13 @@
         <v>0</v>
       </c>
       <c r="O42" s="10" t="n">
-        <v>12700</v>
+        <v>0</v>
       </c>
       <c r="P42" s="10" t="n">
-        <v>1143</v>
+        <v>0</v>
       </c>
       <c r="Q42" s="10" t="n">
-        <v>1143</v>
+        <v>0</v>
       </c>
       <c r="R42" s="10" t="n">
         <v>0</v>
@@ -8270,10 +8258,10 @@
         <v>0</v>
       </c>
       <c r="Z42" s="10" t="n">
-        <v>0</v>
+        <v>919095</v>
       </c>
       <c r="AA42" s="10" t="n">
-        <v>0</v>
+        <v>165437.1</v>
       </c>
       <c r="AB42" s="10" t="n">
         <v>0</v>
@@ -8334,29 +8322,29 @@
       <c r="CB42" s="11" t="n"/>
       <c r="CC42" s="11" t="inlineStr">
         <is>
-          <t>IC/26-27/0904Innovatech Corporation. Done!</t>
+          <t>GPE/2684/25-26Goel Power Engineers LLP. Done!</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>27AHXPG7701J1ZV</t>
+          <t>26AAHFG0858R1ZS</t>
         </is>
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>IC/26-27/0937</t>
+          <t>GPE/2832/25-26</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>15-07-2026</t>
+          <t>29-11-2025</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>Innovatech Corporation</t>
+          <t>Goel Power Engineers LLP</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
@@ -8394,13 +8382,13 @@
         <v>0</v>
       </c>
       <c r="O43" s="10" t="n">
-        <v>18470</v>
+        <v>0</v>
       </c>
       <c r="P43" s="10" t="n">
-        <v>1662.3</v>
+        <v>0</v>
       </c>
       <c r="Q43" s="10" t="n">
-        <v>1662.3</v>
+        <v>0</v>
       </c>
       <c r="R43" s="10" t="n">
         <v>0</v>
@@ -8427,10 +8415,10 @@
         <v>0</v>
       </c>
       <c r="Z43" s="10" t="n">
-        <v>0</v>
+        <v>1445590</v>
       </c>
       <c r="AA43" s="10" t="n">
-        <v>0</v>
+        <v>260206.2</v>
       </c>
       <c r="AB43" s="10" t="n">
         <v>0</v>
@@ -8491,29 +8479,29 @@
       <c r="CB43" s="11" t="n"/>
       <c r="CC43" s="11" t="inlineStr">
         <is>
-          <t>IC/26-27/0937Innovatech Corporation. Done!</t>
+          <t>GPE/2832/25-26Goel Power Engineers LLP. Done!</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>27AHXPG7701J1ZV</t>
+          <t>26AAHFG0858R1ZS</t>
         </is>
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>IC/26-27/1012</t>
+          <t>GPE/2847/25-26</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>22-07-2026</t>
+          <t>29-11-2025</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>Innovatech Corporation</t>
+          <t>Goel Power Engineers LLP</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
@@ -8551,13 +8539,13 @@
         <v>0</v>
       </c>
       <c r="O44" s="10" t="n">
-        <v>8220</v>
+        <v>0</v>
       </c>
       <c r="P44" s="10" t="n">
-        <v>739.8</v>
+        <v>0</v>
       </c>
       <c r="Q44" s="10" t="n">
-        <v>739.8</v>
+        <v>0</v>
       </c>
       <c r="R44" s="10" t="n">
         <v>0</v>
@@ -8584,10 +8572,10 @@
         <v>0</v>
       </c>
       <c r="Z44" s="10" t="n">
-        <v>0</v>
+        <v>593340</v>
       </c>
       <c r="AA44" s="10" t="n">
-        <v>0</v>
+        <v>106801.2</v>
       </c>
       <c r="AB44" s="10" t="n">
         <v>0</v>
@@ -8648,29 +8636,29 @@
       <c r="CB44" s="11" t="n"/>
       <c r="CC44" s="11" t="inlineStr">
         <is>
-          <t>IC/26-27/1012Innovatech Corporation. Done!</t>
+          <t>GPE/2847/25-26Goel Power Engineers LLP. Done!</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>27AIEPM7924K1ZU</t>
+          <t>27AAVFK1861C1Z6</t>
         </is>
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>D/H/26-27/3042</t>
+          <t>INVH/025763</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>27-11-2025</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>Darshak Hardware</t>
+          <t>Keshav Enterprises</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
@@ -8708,13 +8696,13 @@
         <v>0</v>
       </c>
       <c r="O45" s="10" t="n">
-        <v>31965</v>
+        <v>3870.53</v>
       </c>
       <c r="P45" s="10" t="n">
-        <v>2876.85</v>
+        <v>348.35</v>
       </c>
       <c r="Q45" s="10" t="n">
-        <v>2876.85</v>
+        <v>348.35</v>
       </c>
       <c r="R45" s="10" t="n">
         <v>0</v>
@@ -8805,29 +8793,29 @@
       <c r="CB45" s="11" t="n"/>
       <c r="CC45" s="11" t="inlineStr">
         <is>
-          <t>D/H/26-27/3042Darshak Hardware. Done!</t>
+          <t>INVH/025763Keshav Enterprises. Done!</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>27AIEPM7924K1ZU</t>
+          <t>24AABFO6856D1ZD</t>
         </is>
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>D/H/26-27/3747</t>
+          <t>969</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>27-07-2026</t>
+          <t>27-11-2025</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>Darshak Hardware</t>
+          <t>Opera Polymers</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
@@ -8865,13 +8853,13 @@
         <v>0</v>
       </c>
       <c r="O46" s="10" t="n">
-        <v>16252</v>
+        <v>0</v>
       </c>
       <c r="P46" s="10" t="n">
-        <v>1462.68</v>
+        <v>0</v>
       </c>
       <c r="Q46" s="10" t="n">
-        <v>1462.68</v>
+        <v>0</v>
       </c>
       <c r="R46" s="10" t="n">
         <v>0</v>
@@ -8898,10 +8886,10 @@
         <v>0</v>
       </c>
       <c r="Z46" s="10" t="n">
-        <v>0</v>
+        <v>35464.8</v>
       </c>
       <c r="AA46" s="10" t="n">
-        <v>0</v>
+        <v>6383.66</v>
       </c>
       <c r="AB46" s="10" t="n">
         <v>0</v>
@@ -8962,1577 +8950,7 @@
       <c r="CB46" s="11" t="n"/>
       <c r="CC46" s="11" t="inlineStr">
         <is>
-          <t>D/H/26-27/3747Darshak Hardware. Done!</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="9" t="inlineStr">
-        <is>
-          <t>27ATJPS9427R1ZH</t>
-        </is>
-      </c>
-      <c r="B47" s="9" t="inlineStr">
-        <is>
-          <t>2815/26-27</t>
-        </is>
-      </c>
-      <c r="C47" s="9" t="inlineStr">
-        <is>
-          <t>23-07-2026</t>
-        </is>
-      </c>
-      <c r="D47" s="9" t="inlineStr">
-        <is>
-          <t>V N Enterprises</t>
-        </is>
-      </c>
-      <c r="E47" s="9" t="inlineStr">
-        <is>
-          <t>BEING PURCHASE RECORDED</t>
-        </is>
-      </c>
-      <c r="F47" s="9" t="inlineStr">
-        <is>
-          <t>Purchase New</t>
-        </is>
-      </c>
-      <c r="G47" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="H47" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" s="10" t="n">
-        <v>8929.34</v>
-      </c>
-      <c r="P47" s="10" t="n">
-        <v>803.64</v>
-      </c>
-      <c r="Q47" s="10" t="n">
-        <v>803.64</v>
-      </c>
-      <c r="R47" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W47" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X47" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y47" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z47" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA47" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB47" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC47" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD47" s="11" t="n"/>
-      <c r="AE47" s="11" t="n"/>
-      <c r="AF47" s="11" t="n"/>
-      <c r="AG47" s="11" t="n"/>
-      <c r="AH47" s="11" t="n"/>
-      <c r="AI47" s="11" t="n"/>
-      <c r="AJ47" s="11" t="n"/>
-      <c r="AK47" s="11" t="n"/>
-      <c r="AL47" s="11" t="n"/>
-      <c r="AM47" s="11" t="n"/>
-      <c r="AN47" s="11" t="n"/>
-      <c r="AO47" s="11" t="n"/>
-      <c r="AP47" s="11" t="n"/>
-      <c r="AQ47" s="11" t="n"/>
-      <c r="AR47" s="11" t="n"/>
-      <c r="AS47" s="11" t="n"/>
-      <c r="AT47" s="11" t="n"/>
-      <c r="AU47" s="11" t="n"/>
-      <c r="AV47" s="11" t="n"/>
-      <c r="AW47" s="11" t="n"/>
-      <c r="AX47" s="11" t="n"/>
-      <c r="AY47" s="11" t="n"/>
-      <c r="AZ47" s="11" t="n"/>
-      <c r="BA47" s="11" t="n"/>
-      <c r="BB47" s="11" t="n"/>
-      <c r="BC47" s="11" t="n"/>
-      <c r="BD47" s="11" t="n"/>
-      <c r="BE47" s="11" t="n"/>
-      <c r="BF47" s="11" t="n"/>
-      <c r="BG47" s="11" t="n"/>
-      <c r="BH47" s="11" t="n"/>
-      <c r="BI47" s="11" t="n"/>
-      <c r="BJ47" s="11" t="n"/>
-      <c r="BK47" s="11" t="n"/>
-      <c r="BL47" s="11" t="n"/>
-      <c r="BM47" s="11" t="n"/>
-      <c r="BN47" s="11" t="n"/>
-      <c r="BO47" s="11" t="n"/>
-      <c r="BP47" s="11" t="n"/>
-      <c r="BQ47" s="11" t="n"/>
-      <c r="BR47" s="11" t="n"/>
-      <c r="BS47" s="11" t="n"/>
-      <c r="BT47" s="11" t="n"/>
-      <c r="BU47" s="11" t="n"/>
-      <c r="BV47" s="11" t="n"/>
-      <c r="BW47" s="11" t="n"/>
-      <c r="BX47" s="11" t="n"/>
-      <c r="BY47" s="11" t="n"/>
-      <c r="BZ47" s="11" t="n"/>
-      <c r="CA47" s="11" t="n"/>
-      <c r="CB47" s="11" t="n"/>
-      <c r="CC47" s="11" t="inlineStr">
-        <is>
-          <t>2815/26-27V N Enterprises. Done!</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="9" t="inlineStr">
-        <is>
-          <t>27AAVFK1861C1Z6</t>
-        </is>
-      </c>
-      <c r="B48" s="9" t="inlineStr">
-        <is>
-          <t>INVH/036237</t>
-        </is>
-      </c>
-      <c r="C48" s="9" t="inlineStr">
-        <is>
-          <t>13-07-2026</t>
-        </is>
-      </c>
-      <c r="D48" s="9" t="inlineStr">
-        <is>
-          <t>Keshav Enterprises</t>
-        </is>
-      </c>
-      <c r="E48" s="9" t="inlineStr">
-        <is>
-          <t>BEING PURCHASE RECORDED</t>
-        </is>
-      </c>
-      <c r="F48" s="9" t="inlineStr">
-        <is>
-          <t>Purchase New</t>
-        </is>
-      </c>
-      <c r="G48" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="H48" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" s="10" t="n">
-        <v>4532.57</v>
-      </c>
-      <c r="P48" s="10" t="n">
-        <v>407.93</v>
-      </c>
-      <c r="Q48" s="10" t="n">
-        <v>407.93</v>
-      </c>
-      <c r="R48" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W48" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X48" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y48" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z48" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA48" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB48" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC48" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD48" s="11" t="n"/>
-      <c r="AE48" s="11" t="n"/>
-      <c r="AF48" s="11" t="n"/>
-      <c r="AG48" s="11" t="n"/>
-      <c r="AH48" s="11" t="n"/>
-      <c r="AI48" s="11" t="n"/>
-      <c r="AJ48" s="11" t="n"/>
-      <c r="AK48" s="11" t="n"/>
-      <c r="AL48" s="11" t="n"/>
-      <c r="AM48" s="11" t="n"/>
-      <c r="AN48" s="11" t="n"/>
-      <c r="AO48" s="11" t="n"/>
-      <c r="AP48" s="11" t="n"/>
-      <c r="AQ48" s="11" t="n"/>
-      <c r="AR48" s="11" t="n"/>
-      <c r="AS48" s="11" t="n"/>
-      <c r="AT48" s="11" t="n"/>
-      <c r="AU48" s="11" t="n"/>
-      <c r="AV48" s="11" t="n"/>
-      <c r="AW48" s="11" t="n"/>
-      <c r="AX48" s="11" t="n"/>
-      <c r="AY48" s="11" t="n"/>
-      <c r="AZ48" s="11" t="n"/>
-      <c r="BA48" s="11" t="n"/>
-      <c r="BB48" s="11" t="n"/>
-      <c r="BC48" s="11" t="n"/>
-      <c r="BD48" s="11" t="n"/>
-      <c r="BE48" s="11" t="n"/>
-      <c r="BF48" s="11" t="n"/>
-      <c r="BG48" s="11" t="n"/>
-      <c r="BH48" s="11" t="n"/>
-      <c r="BI48" s="11" t="n"/>
-      <c r="BJ48" s="11" t="n"/>
-      <c r="BK48" s="11" t="n"/>
-      <c r="BL48" s="11" t="n"/>
-      <c r="BM48" s="11" t="n"/>
-      <c r="BN48" s="11" t="n"/>
-      <c r="BO48" s="11" t="n"/>
-      <c r="BP48" s="11" t="n"/>
-      <c r="BQ48" s="11" t="n"/>
-      <c r="BR48" s="11" t="n"/>
-      <c r="BS48" s="11" t="n"/>
-      <c r="BT48" s="11" t="n"/>
-      <c r="BU48" s="11" t="n"/>
-      <c r="BV48" s="11" t="n"/>
-      <c r="BW48" s="11" t="n"/>
-      <c r="BX48" s="11" t="n"/>
-      <c r="BY48" s="11" t="n"/>
-      <c r="BZ48" s="11" t="n"/>
-      <c r="CA48" s="11" t="n"/>
-      <c r="CB48" s="11" t="n"/>
-      <c r="CC48" s="11" t="inlineStr">
-        <is>
-          <t>INVH/036237Keshav Enterprises. Done!</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="9" t="inlineStr">
-        <is>
-          <t>27AACPD2331D1ZI</t>
-        </is>
-      </c>
-      <c r="B49" s="9" t="inlineStr">
-        <is>
-          <t>SG-1417</t>
-        </is>
-      </c>
-      <c r="C49" s="9" t="inlineStr">
-        <is>
-          <t>27-07-2026</t>
-        </is>
-      </c>
-      <c r="D49" s="9" t="inlineStr">
-        <is>
-          <t>Shubham Enterprise</t>
-        </is>
-      </c>
-      <c r="E49" s="9" t="inlineStr">
-        <is>
-          <t>BEING PURCHASE RECORDED</t>
-        </is>
-      </c>
-      <c r="F49" s="9" t="inlineStr">
-        <is>
-          <t>Purchase New</t>
-        </is>
-      </c>
-      <c r="G49" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="H49" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" s="10" t="n">
-        <v>7195.5</v>
-      </c>
-      <c r="P49" s="10" t="n">
-        <v>647.6</v>
-      </c>
-      <c r="Q49" s="10" t="n">
-        <v>647.6</v>
-      </c>
-      <c r="R49" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W49" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X49" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y49" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z49" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA49" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB49" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC49" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD49" s="11" t="n"/>
-      <c r="AE49" s="11" t="n"/>
-      <c r="AF49" s="11" t="n"/>
-      <c r="AG49" s="11" t="n"/>
-      <c r="AH49" s="11" t="n"/>
-      <c r="AI49" s="11" t="n"/>
-      <c r="AJ49" s="11" t="n"/>
-      <c r="AK49" s="11" t="n"/>
-      <c r="AL49" s="11" t="n"/>
-      <c r="AM49" s="11" t="n"/>
-      <c r="AN49" s="11" t="n"/>
-      <c r="AO49" s="11" t="n"/>
-      <c r="AP49" s="11" t="n"/>
-      <c r="AQ49" s="11" t="n"/>
-      <c r="AR49" s="11" t="n"/>
-      <c r="AS49" s="11" t="n"/>
-      <c r="AT49" s="11" t="n"/>
-      <c r="AU49" s="11" t="n"/>
-      <c r="AV49" s="11" t="n"/>
-      <c r="AW49" s="11" t="n"/>
-      <c r="AX49" s="11" t="n"/>
-      <c r="AY49" s="11" t="n"/>
-      <c r="AZ49" s="11" t="n"/>
-      <c r="BA49" s="11" t="n"/>
-      <c r="BB49" s="11" t="n"/>
-      <c r="BC49" s="11" t="n"/>
-      <c r="BD49" s="11" t="n"/>
-      <c r="BE49" s="11" t="n"/>
-      <c r="BF49" s="11" t="n"/>
-      <c r="BG49" s="11" t="n"/>
-      <c r="BH49" s="11" t="n"/>
-      <c r="BI49" s="11" t="n"/>
-      <c r="BJ49" s="11" t="n"/>
-      <c r="BK49" s="11" t="n"/>
-      <c r="BL49" s="11" t="n"/>
-      <c r="BM49" s="11" t="n"/>
-      <c r="BN49" s="11" t="n"/>
-      <c r="BO49" s="11" t="n"/>
-      <c r="BP49" s="11" t="n"/>
-      <c r="BQ49" s="11" t="n"/>
-      <c r="BR49" s="11" t="n"/>
-      <c r="BS49" s="11" t="n"/>
-      <c r="BT49" s="11" t="n"/>
-      <c r="BU49" s="11" t="n"/>
-      <c r="BV49" s="11" t="n"/>
-      <c r="BW49" s="11" t="n"/>
-      <c r="BX49" s="11" t="n"/>
-      <c r="BY49" s="11" t="n"/>
-      <c r="BZ49" s="11" t="n"/>
-      <c r="CA49" s="11" t="n"/>
-      <c r="CB49" s="11" t="n"/>
-      <c r="CC49" s="11" t="inlineStr">
-        <is>
-          <t>SG-1417Shubham Enterprise. Done!</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="9" t="inlineStr">
-        <is>
-          <t>27AJHPM6470C1Z7</t>
-        </is>
-      </c>
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t>S00568/26-27</t>
-        </is>
-      </c>
-      <c r="C50" s="9" t="inlineStr">
-        <is>
-          <t>29-07-2026</t>
-        </is>
-      </c>
-      <c r="D50" s="9" t="inlineStr">
-        <is>
-          <t>Mihir Sales</t>
-        </is>
-      </c>
-      <c r="E50" s="9" t="inlineStr">
-        <is>
-          <t>BEING PURCHASE RECORDED</t>
-        </is>
-      </c>
-      <c r="F50" s="9" t="inlineStr">
-        <is>
-          <t>Purchase New</t>
-        </is>
-      </c>
-      <c r="G50" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="H50" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" s="10" t="n">
-        <v>23103.7</v>
-      </c>
-      <c r="P50" s="10" t="n">
-        <v>2079.33</v>
-      </c>
-      <c r="Q50" s="10" t="n">
-        <v>2079.33</v>
-      </c>
-      <c r="R50" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W50" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X50" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y50" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z50" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA50" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB50" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC50" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD50" s="11" t="n"/>
-      <c r="AE50" s="11" t="n"/>
-      <c r="AF50" s="11" t="n"/>
-      <c r="AG50" s="11" t="n"/>
-      <c r="AH50" s="11" t="n"/>
-      <c r="AI50" s="11" t="n"/>
-      <c r="AJ50" s="11" t="n"/>
-      <c r="AK50" s="11" t="n"/>
-      <c r="AL50" s="11" t="n"/>
-      <c r="AM50" s="11" t="n"/>
-      <c r="AN50" s="11" t="n"/>
-      <c r="AO50" s="11" t="n"/>
-      <c r="AP50" s="11" t="n"/>
-      <c r="AQ50" s="11" t="n"/>
-      <c r="AR50" s="11" t="n"/>
-      <c r="AS50" s="11" t="n"/>
-      <c r="AT50" s="11" t="n"/>
-      <c r="AU50" s="11" t="n"/>
-      <c r="AV50" s="11" t="n"/>
-      <c r="AW50" s="11" t="n"/>
-      <c r="AX50" s="11" t="n"/>
-      <c r="AY50" s="11" t="n"/>
-      <c r="AZ50" s="11" t="n"/>
-      <c r="BA50" s="11" t="n"/>
-      <c r="BB50" s="11" t="n"/>
-      <c r="BC50" s="11" t="n"/>
-      <c r="BD50" s="11" t="n"/>
-      <c r="BE50" s="11" t="n"/>
-      <c r="BF50" s="11" t="n"/>
-      <c r="BG50" s="11" t="n"/>
-      <c r="BH50" s="11" t="n"/>
-      <c r="BI50" s="11" t="n"/>
-      <c r="BJ50" s="11" t="n"/>
-      <c r="BK50" s="11" t="n"/>
-      <c r="BL50" s="11" t="n"/>
-      <c r="BM50" s="11" t="n"/>
-      <c r="BN50" s="11" t="n"/>
-      <c r="BO50" s="11" t="n"/>
-      <c r="BP50" s="11" t="n"/>
-      <c r="BQ50" s="11" t="n"/>
-      <c r="BR50" s="11" t="n"/>
-      <c r="BS50" s="11" t="n"/>
-      <c r="BT50" s="11" t="n"/>
-      <c r="BU50" s="11" t="n"/>
-      <c r="BV50" s="11" t="n"/>
-      <c r="BW50" s="11" t="n"/>
-      <c r="BX50" s="11" t="n"/>
-      <c r="BY50" s="11" t="n"/>
-      <c r="BZ50" s="11" t="n"/>
-      <c r="CA50" s="11" t="n"/>
-      <c r="CB50" s="11" t="n"/>
-      <c r="CC50" s="11" t="inlineStr">
-        <is>
-          <t>S00568/26-27Mihir Sales. Done!</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="9" t="inlineStr">
-        <is>
-          <t>27AAACT5626Q1ZS</t>
-        </is>
-      </c>
-      <c r="B51" s="9" t="inlineStr">
-        <is>
-          <t>S419912062700704</t>
-        </is>
-      </c>
-      <c r="C51" s="9" t="inlineStr">
-        <is>
-          <t>07-07-2026</t>
-        </is>
-      </c>
-      <c r="D51" s="9" t="inlineStr">
-        <is>
-          <t>Transcreek Engineers PVT LTD</t>
-        </is>
-      </c>
-      <c r="E51" s="9" t="inlineStr">
-        <is>
-          <t>BEING PURCHASE RECORDED</t>
-        </is>
-      </c>
-      <c r="F51" s="9" t="inlineStr">
-        <is>
-          <t>Purchase New</t>
-        </is>
-      </c>
-      <c r="G51" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="H51" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" s="10" t="n">
-        <v>88145.28</v>
-      </c>
-      <c r="P51" s="10" t="n">
-        <v>7933.07</v>
-      </c>
-      <c r="Q51" s="10" t="n">
-        <v>7933.07</v>
-      </c>
-      <c r="R51" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W51" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X51" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y51" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z51" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA51" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB51" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC51" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD51" s="11" t="n"/>
-      <c r="AE51" s="11" t="n"/>
-      <c r="AF51" s="11" t="n"/>
-      <c r="AG51" s="11" t="n"/>
-      <c r="AH51" s="11" t="n"/>
-      <c r="AI51" s="11" t="n"/>
-      <c r="AJ51" s="11" t="n"/>
-      <c r="AK51" s="11" t="n"/>
-      <c r="AL51" s="11" t="n"/>
-      <c r="AM51" s="11" t="n"/>
-      <c r="AN51" s="11" t="n"/>
-      <c r="AO51" s="11" t="n"/>
-      <c r="AP51" s="11" t="n"/>
-      <c r="AQ51" s="11" t="n"/>
-      <c r="AR51" s="11" t="n"/>
-      <c r="AS51" s="11" t="n"/>
-      <c r="AT51" s="11" t="n"/>
-      <c r="AU51" s="11" t="n"/>
-      <c r="AV51" s="11" t="n"/>
-      <c r="AW51" s="11" t="n"/>
-      <c r="AX51" s="11" t="n"/>
-      <c r="AY51" s="11" t="n"/>
-      <c r="AZ51" s="11" t="n"/>
-      <c r="BA51" s="11" t="n"/>
-      <c r="BB51" s="11" t="n"/>
-      <c r="BC51" s="11" t="n"/>
-      <c r="BD51" s="11" t="n"/>
-      <c r="BE51" s="11" t="n"/>
-      <c r="BF51" s="11" t="n"/>
-      <c r="BG51" s="11" t="n"/>
-      <c r="BH51" s="11" t="n"/>
-      <c r="BI51" s="11" t="n"/>
-      <c r="BJ51" s="11" t="n"/>
-      <c r="BK51" s="11" t="n"/>
-      <c r="BL51" s="11" t="n"/>
-      <c r="BM51" s="11" t="n"/>
-      <c r="BN51" s="11" t="n"/>
-      <c r="BO51" s="11" t="n"/>
-      <c r="BP51" s="11" t="n"/>
-      <c r="BQ51" s="11" t="n"/>
-      <c r="BR51" s="11" t="n"/>
-      <c r="BS51" s="11" t="n"/>
-      <c r="BT51" s="11" t="n"/>
-      <c r="BU51" s="11" t="n"/>
-      <c r="BV51" s="11" t="n"/>
-      <c r="BW51" s="11" t="n"/>
-      <c r="BX51" s="11" t="n"/>
-      <c r="BY51" s="11" t="n"/>
-      <c r="BZ51" s="11" t="n"/>
-      <c r="CA51" s="11" t="n"/>
-      <c r="CB51" s="11" t="n"/>
-      <c r="CC51" s="11" t="inlineStr">
-        <is>
-          <t>S419912062700704Transcreek Engineers PVT LTD. Done!</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="9" t="inlineStr">
-        <is>
-          <t>24AAHFJ5991L1ZT</t>
-        </is>
-      </c>
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t>GT/11</t>
-        </is>
-      </c>
-      <c r="C52" s="9" t="inlineStr">
-        <is>
-          <t>09-07-2026</t>
-        </is>
-      </c>
-      <c r="D52" s="9" t="inlineStr">
-        <is>
-          <t>J.p.diesel</t>
-        </is>
-      </c>
-      <c r="E52" s="9" t="inlineStr">
-        <is>
-          <t>BEING PURCHASE RECORDED</t>
-        </is>
-      </c>
-      <c r="F52" s="9" t="inlineStr">
-        <is>
-          <t>Purchase New</t>
-        </is>
-      </c>
-      <c r="G52" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="H52" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U52" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W52" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X52" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y52" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z52" s="10" t="n">
-        <v>96500</v>
-      </c>
-      <c r="AA52" s="10" t="n">
-        <v>14510</v>
-      </c>
-      <c r="AB52" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC52" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD52" s="11" t="n"/>
-      <c r="AE52" s="11" t="n"/>
-      <c r="AF52" s="11" t="n"/>
-      <c r="AG52" s="11" t="n"/>
-      <c r="AH52" s="11" t="n"/>
-      <c r="AI52" s="11" t="n"/>
-      <c r="AJ52" s="11" t="n"/>
-      <c r="AK52" s="11" t="n"/>
-      <c r="AL52" s="11" t="n"/>
-      <c r="AM52" s="11" t="n"/>
-      <c r="AN52" s="11" t="n"/>
-      <c r="AO52" s="11" t="n"/>
-      <c r="AP52" s="11" t="n"/>
-      <c r="AQ52" s="11" t="n"/>
-      <c r="AR52" s="11" t="n"/>
-      <c r="AS52" s="11" t="n"/>
-      <c r="AT52" s="11" t="n"/>
-      <c r="AU52" s="11" t="n"/>
-      <c r="AV52" s="11" t="n"/>
-      <c r="AW52" s="11" t="n"/>
-      <c r="AX52" s="11" t="n"/>
-      <c r="AY52" s="11" t="n"/>
-      <c r="AZ52" s="11" t="n"/>
-      <c r="BA52" s="11" t="n"/>
-      <c r="BB52" s="11" t="n"/>
-      <c r="BC52" s="11" t="n"/>
-      <c r="BD52" s="11" t="n"/>
-      <c r="BE52" s="11" t="n"/>
-      <c r="BF52" s="11" t="n"/>
-      <c r="BG52" s="11" t="n"/>
-      <c r="BH52" s="11" t="n"/>
-      <c r="BI52" s="11" t="n"/>
-      <c r="BJ52" s="11" t="n"/>
-      <c r="BK52" s="11" t="n"/>
-      <c r="BL52" s="11" t="n"/>
-      <c r="BM52" s="11" t="n"/>
-      <c r="BN52" s="11" t="n"/>
-      <c r="BO52" s="11" t="n"/>
-      <c r="BP52" s="11" t="n"/>
-      <c r="BQ52" s="11" t="n"/>
-      <c r="BR52" s="11" t="n"/>
-      <c r="BS52" s="11" t="n"/>
-      <c r="BT52" s="11" t="n"/>
-      <c r="BU52" s="11" t="n"/>
-      <c r="BV52" s="11" t="n"/>
-      <c r="BW52" s="11" t="n"/>
-      <c r="BX52" s="11" t="n"/>
-      <c r="BY52" s="11" t="n"/>
-      <c r="BZ52" s="11" t="n"/>
-      <c r="CA52" s="11" t="n"/>
-      <c r="CB52" s="11" t="n"/>
-      <c r="CC52" s="11" t="inlineStr">
-        <is>
-          <t>GT/11J.p.diesel. Done!</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="9" t="inlineStr">
-        <is>
-          <t>24AAHFJ5991L1ZT</t>
-        </is>
-      </c>
-      <c r="B53" s="9" t="inlineStr">
-        <is>
-          <t>GT/13</t>
-        </is>
-      </c>
-      <c r="C53" s="9" t="inlineStr">
-        <is>
-          <t>23-07-2026</t>
-        </is>
-      </c>
-      <c r="D53" s="9" t="inlineStr">
-        <is>
-          <t>J.p.diesel</t>
-        </is>
-      </c>
-      <c r="E53" s="9" t="inlineStr">
-        <is>
-          <t>BEING PURCHASE RECORDED</t>
-        </is>
-      </c>
-      <c r="F53" s="9" t="inlineStr">
-        <is>
-          <t>Purchase New</t>
-        </is>
-      </c>
-      <c r="G53" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="H53" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W53" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X53" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y53" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z53" s="10" t="n">
-        <v>80000</v>
-      </c>
-      <c r="AA53" s="10" t="n">
-        <v>14400</v>
-      </c>
-      <c r="AB53" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC53" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD53" s="11" t="n"/>
-      <c r="AE53" s="11" t="n"/>
-      <c r="AF53" s="11" t="n"/>
-      <c r="AG53" s="11" t="n"/>
-      <c r="AH53" s="11" t="n"/>
-      <c r="AI53" s="11" t="n"/>
-      <c r="AJ53" s="11" t="n"/>
-      <c r="AK53" s="11" t="n"/>
-      <c r="AL53" s="11" t="n"/>
-      <c r="AM53" s="11" t="n"/>
-      <c r="AN53" s="11" t="n"/>
-      <c r="AO53" s="11" t="n"/>
-      <c r="AP53" s="11" t="n"/>
-      <c r="AQ53" s="11" t="n"/>
-      <c r="AR53" s="11" t="n"/>
-      <c r="AS53" s="11" t="n"/>
-      <c r="AT53" s="11" t="n"/>
-      <c r="AU53" s="11" t="n"/>
-      <c r="AV53" s="11" t="n"/>
-      <c r="AW53" s="11" t="n"/>
-      <c r="AX53" s="11" t="n"/>
-      <c r="AY53" s="11" t="n"/>
-      <c r="AZ53" s="11" t="n"/>
-      <c r="BA53" s="11" t="n"/>
-      <c r="BB53" s="11" t="n"/>
-      <c r="BC53" s="11" t="n"/>
-      <c r="BD53" s="11" t="n"/>
-      <c r="BE53" s="11" t="n"/>
-      <c r="BF53" s="11" t="n"/>
-      <c r="BG53" s="11" t="n"/>
-      <c r="BH53" s="11" t="n"/>
-      <c r="BI53" s="11" t="n"/>
-      <c r="BJ53" s="11" t="n"/>
-      <c r="BK53" s="11" t="n"/>
-      <c r="BL53" s="11" t="n"/>
-      <c r="BM53" s="11" t="n"/>
-      <c r="BN53" s="11" t="n"/>
-      <c r="BO53" s="11" t="n"/>
-      <c r="BP53" s="11" t="n"/>
-      <c r="BQ53" s="11" t="n"/>
-      <c r="BR53" s="11" t="n"/>
-      <c r="BS53" s="11" t="n"/>
-      <c r="BT53" s="11" t="n"/>
-      <c r="BU53" s="11" t="n"/>
-      <c r="BV53" s="11" t="n"/>
-      <c r="BW53" s="11" t="n"/>
-      <c r="BX53" s="11" t="n"/>
-      <c r="BY53" s="11" t="n"/>
-      <c r="BZ53" s="11" t="n"/>
-      <c r="CA53" s="11" t="n"/>
-      <c r="CB53" s="11" t="n"/>
-      <c r="CC53" s="11" t="inlineStr">
-        <is>
-          <t>GT/13J.p.diesel. Done!</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="9" t="inlineStr">
-        <is>
-          <t>06BIOPS2704Q1ZL</t>
-        </is>
-      </c>
-      <c r="B54" s="9" t="inlineStr">
-        <is>
-          <t>26-27/00514</t>
-        </is>
-      </c>
-      <c r="C54" s="9" t="inlineStr">
-        <is>
-          <t>27-07-2026</t>
-        </is>
-      </c>
-      <c r="D54" s="9" t="inlineStr">
-        <is>
-          <t>Automation Electronics</t>
-        </is>
-      </c>
-      <c r="E54" s="9" t="inlineStr">
-        <is>
-          <t>BEING PURCHASE RECORDED</t>
-        </is>
-      </c>
-      <c r="F54" s="9" t="inlineStr">
-        <is>
-          <t>Purchase New</t>
-        </is>
-      </c>
-      <c r="G54" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="H54" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V54" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W54" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X54" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y54" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z54" s="10" t="n">
-        <v>20000</v>
-      </c>
-      <c r="AA54" s="10" t="n">
-        <v>3600</v>
-      </c>
-      <c r="AB54" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC54" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD54" s="11" t="n"/>
-      <c r="AE54" s="11" t="n"/>
-      <c r="AF54" s="11" t="n"/>
-      <c r="AG54" s="11" t="n"/>
-      <c r="AH54" s="11" t="n"/>
-      <c r="AI54" s="11" t="n"/>
-      <c r="AJ54" s="11" t="n"/>
-      <c r="AK54" s="11" t="n"/>
-      <c r="AL54" s="11" t="n"/>
-      <c r="AM54" s="11" t="n"/>
-      <c r="AN54" s="11" t="n"/>
-      <c r="AO54" s="11" t="n"/>
-      <c r="AP54" s="11" t="n"/>
-      <c r="AQ54" s="11" t="n"/>
-      <c r="AR54" s="11" t="n"/>
-      <c r="AS54" s="11" t="n"/>
-      <c r="AT54" s="11" t="n"/>
-      <c r="AU54" s="11" t="n"/>
-      <c r="AV54" s="11" t="n"/>
-      <c r="AW54" s="11" t="n"/>
-      <c r="AX54" s="11" t="n"/>
-      <c r="AY54" s="11" t="n"/>
-      <c r="AZ54" s="11" t="n"/>
-      <c r="BA54" s="11" t="n"/>
-      <c r="BB54" s="11" t="n"/>
-      <c r="BC54" s="11" t="n"/>
-      <c r="BD54" s="11" t="n"/>
-      <c r="BE54" s="11" t="n"/>
-      <c r="BF54" s="11" t="n"/>
-      <c r="BG54" s="11" t="n"/>
-      <c r="BH54" s="11" t="n"/>
-      <c r="BI54" s="11" t="n"/>
-      <c r="BJ54" s="11" t="n"/>
-      <c r="BK54" s="11" t="n"/>
-      <c r="BL54" s="11" t="n"/>
-      <c r="BM54" s="11" t="n"/>
-      <c r="BN54" s="11" t="n"/>
-      <c r="BO54" s="11" t="n"/>
-      <c r="BP54" s="11" t="n"/>
-      <c r="BQ54" s="11" t="n"/>
-      <c r="BR54" s="11" t="n"/>
-      <c r="BS54" s="11" t="n"/>
-      <c r="BT54" s="11" t="n"/>
-      <c r="BU54" s="11" t="n"/>
-      <c r="BV54" s="11" t="n"/>
-      <c r="BW54" s="11" t="n"/>
-      <c r="BX54" s="11" t="n"/>
-      <c r="BY54" s="11" t="n"/>
-      <c r="BZ54" s="11" t="n"/>
-      <c r="CA54" s="11" t="n"/>
-      <c r="CB54" s="11" t="n"/>
-      <c r="CC54" s="11" t="inlineStr">
-        <is>
-          <t>26-27/00514Automation Electronics. Done!</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="9" t="inlineStr">
-        <is>
-          <t>27AAGCV9302B1ZI</t>
-        </is>
-      </c>
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t>VZE/450/2026-27</t>
-        </is>
-      </c>
-      <c r="C55" s="9" t="inlineStr">
-        <is>
-          <t>18-07-2026</t>
-        </is>
-      </c>
-      <c r="D55" s="9" t="inlineStr">
-        <is>
-          <t>Veraizen Earthing Private Limited</t>
-        </is>
-      </c>
-      <c r="E55" s="9" t="inlineStr">
-        <is>
-          <t>BEING PURCHASE RECORDED</t>
-        </is>
-      </c>
-      <c r="F55" s="9" t="inlineStr">
-        <is>
-          <t>Purchase New</t>
-        </is>
-      </c>
-      <c r="G55" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="H55" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" s="10" t="n">
-        <v>17028</v>
-      </c>
-      <c r="P55" s="10" t="n">
-        <v>1532.52</v>
-      </c>
-      <c r="Q55" s="10" t="n">
-        <v>1532.52</v>
-      </c>
-      <c r="R55" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W55" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X55" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y55" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z55" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA55" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB55" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC55" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD55" s="11" t="n"/>
-      <c r="AE55" s="11" t="n"/>
-      <c r="AF55" s="11" t="n"/>
-      <c r="AG55" s="11" t="n"/>
-      <c r="AH55" s="11" t="n"/>
-      <c r="AI55" s="11" t="n"/>
-      <c r="AJ55" s="11" t="n"/>
-      <c r="AK55" s="11" t="n"/>
-      <c r="AL55" s="11" t="n"/>
-      <c r="AM55" s="11" t="n"/>
-      <c r="AN55" s="11" t="n"/>
-      <c r="AO55" s="11" t="n"/>
-      <c r="AP55" s="11" t="n"/>
-      <c r="AQ55" s="11" t="n"/>
-      <c r="AR55" s="11" t="n"/>
-      <c r="AS55" s="11" t="n"/>
-      <c r="AT55" s="11" t="n"/>
-      <c r="AU55" s="11" t="n"/>
-      <c r="AV55" s="11" t="n"/>
-      <c r="AW55" s="11" t="n"/>
-      <c r="AX55" s="11" t="n"/>
-      <c r="AY55" s="11" t="n"/>
-      <c r="AZ55" s="11" t="n"/>
-      <c r="BA55" s="11" t="n"/>
-      <c r="BB55" s="11" t="n"/>
-      <c r="BC55" s="11" t="n"/>
-      <c r="BD55" s="11" t="n"/>
-      <c r="BE55" s="11" t="n"/>
-      <c r="BF55" s="11" t="n"/>
-      <c r="BG55" s="11" t="n"/>
-      <c r="BH55" s="11" t="n"/>
-      <c r="BI55" s="11" t="n"/>
-      <c r="BJ55" s="11" t="n"/>
-      <c r="BK55" s="11" t="n"/>
-      <c r="BL55" s="11" t="n"/>
-      <c r="BM55" s="11" t="n"/>
-      <c r="BN55" s="11" t="n"/>
-      <c r="BO55" s="11" t="n"/>
-      <c r="BP55" s="11" t="n"/>
-      <c r="BQ55" s="11" t="n"/>
-      <c r="BR55" s="11" t="n"/>
-      <c r="BS55" s="11" t="n"/>
-      <c r="BT55" s="11" t="n"/>
-      <c r="BU55" s="11" t="n"/>
-      <c r="BV55" s="11" t="n"/>
-      <c r="BW55" s="11" t="n"/>
-      <c r="BX55" s="11" t="n"/>
-      <c r="BY55" s="11" t="n"/>
-      <c r="BZ55" s="11" t="n"/>
-      <c r="CA55" s="11" t="n"/>
-      <c r="CB55" s="11" t="n"/>
-      <c r="CC55" s="11" t="inlineStr">
-        <is>
-          <t>VZE/450/2026-27Veraizen Earthing Private Limited. Done!</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="9" t="inlineStr">
-        <is>
-          <t>27AAGCV9302B1ZI</t>
-        </is>
-      </c>
-      <c r="B56" s="9" t="inlineStr">
-        <is>
-          <t>VZE/451/2026-27</t>
-        </is>
-      </c>
-      <c r="C56" s="9" t="inlineStr">
-        <is>
-          <t>18-07-2026</t>
-        </is>
-      </c>
-      <c r="D56" s="9" t="inlineStr">
-        <is>
-          <t>Veraizen Earthing Private Limited</t>
-        </is>
-      </c>
-      <c r="E56" s="9" t="inlineStr">
-        <is>
-          <t>BEING PURCHASE RECORDED</t>
-        </is>
-      </c>
-      <c r="F56" s="9" t="inlineStr">
-        <is>
-          <t>Purchase New</t>
-        </is>
-      </c>
-      <c r="G56" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="H56" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="10" t="n">
-        <v>16228</v>
-      </c>
-      <c r="P56" s="10" t="n">
-        <v>1460.52</v>
-      </c>
-      <c r="Q56" s="10" t="n">
-        <v>1460.52</v>
-      </c>
-      <c r="R56" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W56" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X56" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y56" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z56" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA56" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB56" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC56" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD56" s="11" t="n"/>
-      <c r="AE56" s="11" t="n"/>
-      <c r="AF56" s="11" t="n"/>
-      <c r="AG56" s="11" t="n"/>
-      <c r="AH56" s="11" t="n"/>
-      <c r="AI56" s="11" t="n"/>
-      <c r="AJ56" s="11" t="n"/>
-      <c r="AK56" s="11" t="n"/>
-      <c r="AL56" s="11" t="n"/>
-      <c r="AM56" s="11" t="n"/>
-      <c r="AN56" s="11" t="n"/>
-      <c r="AO56" s="11" t="n"/>
-      <c r="AP56" s="11" t="n"/>
-      <c r="AQ56" s="11" t="n"/>
-      <c r="AR56" s="11" t="n"/>
-      <c r="AS56" s="11" t="n"/>
-      <c r="AT56" s="11" t="n"/>
-      <c r="AU56" s="11" t="n"/>
-      <c r="AV56" s="11" t="n"/>
-      <c r="AW56" s="11" t="n"/>
-      <c r="AX56" s="11" t="n"/>
-      <c r="AY56" s="11" t="n"/>
-      <c r="AZ56" s="11" t="n"/>
-      <c r="BA56" s="11" t="n"/>
-      <c r="BB56" s="11" t="n"/>
-      <c r="BC56" s="11" t="n"/>
-      <c r="BD56" s="11" t="n"/>
-      <c r="BE56" s="11" t="n"/>
-      <c r="BF56" s="11" t="n"/>
-      <c r="BG56" s="11" t="n"/>
-      <c r="BH56" s="11" t="n"/>
-      <c r="BI56" s="11" t="n"/>
-      <c r="BJ56" s="11" t="n"/>
-      <c r="BK56" s="11" t="n"/>
-      <c r="BL56" s="11" t="n"/>
-      <c r="BM56" s="11" t="n"/>
-      <c r="BN56" s="11" t="n"/>
-      <c r="BO56" s="11" t="n"/>
-      <c r="BP56" s="11" t="n"/>
-      <c r="BQ56" s="11" t="n"/>
-      <c r="BR56" s="11" t="n"/>
-      <c r="BS56" s="11" t="n"/>
-      <c r="BT56" s="11" t="n"/>
-      <c r="BU56" s="11" t="n"/>
-      <c r="BV56" s="11" t="n"/>
-      <c r="BW56" s="11" t="n"/>
-      <c r="BX56" s="11" t="n"/>
-      <c r="BY56" s="11" t="n"/>
-      <c r="BZ56" s="11" t="n"/>
-      <c r="CA56" s="11" t="n"/>
-      <c r="CB56" s="11" t="n"/>
-      <c r="CC56" s="11" t="inlineStr">
-        <is>
-          <t>VZE/451/2026-27Veraizen Earthing Private Limited. Done!</t>
+          <t>969Opera Polymers. Done!</t>
         </is>
       </c>
     </row>
@@ -10552,16 +8970,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="153" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="79" customWidth="1" min="6" max="6"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="12" t="inlineStr">
@@ -10592,66 +9002,6 @@
       <c r="F1" s="12" t="inlineStr">
         <is>
           <t>Suggested Fix</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="13" t="n">
-        <v>16</v>
-      </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>DE/26-27/382</t>
-        </is>
-      </c>
-      <c r="C2" s="13" t="inlineStr">
-        <is>
-          <t>27BRJPD4858C1ZT</t>
-        </is>
-      </c>
-      <c r="D2" s="13" t="inlineStr">
-        <is>
-          <t>CGST 306.91 does not match expected 214.35 for taxable value 8574.0 @ 5%; SGST 306.91 does not match expected 214.35 for taxable value 8574.0 @ 5%</t>
-        </is>
-      </c>
-      <c r="E2" s="14" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="F2" s="13" t="inlineStr">
-        <is>
-          <t>Recheck CGST/SGST against the taxable value and rate for calculation errors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="13" t="n">
-        <v>31</v>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>SG-20126</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>27AILPP4508M1ZQ</t>
-        </is>
-      </c>
-      <c r="D3" s="13" t="inlineStr">
-        <is>
-          <t>CGST 679.19 does not match expected 755.04 for taxable value 12584.0 @ 12%; SGST 679.19 does not match expected 755.04 for taxable value 12584.0 @ 12%</t>
-        </is>
-      </c>
-      <c r="E3" s="14" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="F3" s="13" t="inlineStr">
-        <is>
-          <t>Recheck CGST/SGST against the taxable value and rate for calculation errors.</t>
         </is>
       </c>
     </row>
